--- a/docs/Mapping_casi_uso/morte/Morte_008.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="222">
   <si>
     <t>Sezione</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -730,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1095,7 +1101,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>28</v>
@@ -1141,7 +1147,7 @@
         <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>28</v>
@@ -1273,22 +1279,22 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>18</v>
@@ -1296,16 +1302,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1319,22 +1325,22 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>18</v>
@@ -1342,7 +1348,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
@@ -1351,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1365,7 +1371,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
@@ -1374,10 +1380,10 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1388,16 +1394,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1411,7 +1417,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1420,13 +1426,13 @@
         <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>18</v>
@@ -1434,7 +1440,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1443,13 +1449,13 @@
         <v>27</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>18</v>
@@ -1457,7 +1463,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1466,13 +1472,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>18</v>
@@ -1480,7 +1486,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>79</v>
@@ -1489,13 +1495,13 @@
         <v>27</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>18</v>
@@ -1503,19 +1509,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1526,19 +1532,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1549,16 +1555,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>87</v>
@@ -1572,16 +1578,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>89</v>
@@ -1595,7 +1601,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>90</v>
@@ -1604,7 +1610,7 @@
         <v>27</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>91</v>
@@ -1618,16 +1624,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>93</v>
@@ -1641,16 +1647,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>95</v>
@@ -1664,7 +1670,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>96</v>
@@ -1673,7 +1679,7 @@
         <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>97</v>
@@ -1687,16 +1693,16 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>99</v>
@@ -1710,7 +1716,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>100</v>
@@ -1719,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>101</v>
@@ -1733,7 +1739,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>102</v>
@@ -1742,7 +1748,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>103</v>
@@ -1756,16 +1762,16 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>105</v>
@@ -1779,7 +1785,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>106</v>
@@ -1788,7 +1794,7 @@
         <v>27</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>107</v>
@@ -1802,7 +1808,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>108</v>
@@ -1811,7 +1817,7 @@
         <v>27</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>109</v>
@@ -1825,7 +1831,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1834,7 +1840,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>111</v>
@@ -1848,19 +1854,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1871,16 +1877,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1894,7 +1900,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1903,7 +1909,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1917,16 +1923,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1940,7 +1946,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>119</v>
@@ -1949,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>120</v>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>121</v>
@@ -1972,7 +1978,7 @@
         <v>27</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>122</v>
@@ -1986,7 +1992,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>123</v>
@@ -1995,7 +2001,7 @@
         <v>27</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>124</v>
@@ -2009,7 +2015,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>125</v>
@@ -2018,7 +2024,7 @@
         <v>27</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>126</v>
@@ -2032,7 +2038,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>127</v>
@@ -2041,7 +2047,7 @@
         <v>27</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>128</v>
@@ -2055,7 +2061,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>129</v>
@@ -2064,7 +2070,7 @@
         <v>27</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>130</v>
@@ -2078,7 +2084,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>131</v>
@@ -2087,7 +2093,7 @@
         <v>27</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>132</v>
@@ -2101,7 +2107,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>133</v>
@@ -2110,7 +2116,7 @@
         <v>27</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>134</v>
@@ -2124,7 +2130,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>135</v>
@@ -2133,7 +2139,7 @@
         <v>27</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>136</v>
@@ -2147,7 +2153,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>137</v>
@@ -2156,7 +2162,7 @@
         <v>27</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>138</v>
@@ -2170,7 +2176,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>139</v>
@@ -2179,7 +2185,7 @@
         <v>27</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>140</v>
@@ -2193,39 +2199,39 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="C64" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>87</v>
@@ -2234,35 +2240,35 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>92</v>
@@ -2271,7 +2277,7 @@
         <v>27</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>93</v>
@@ -2280,12 +2286,12 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>94</v>
@@ -2294,7 +2300,7 @@
         <v>27</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>95</v>
@@ -2303,12 +2309,12 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>96</v>
@@ -2317,7 +2323,7 @@
         <v>27</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>97</v>
@@ -2326,12 +2332,12 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>98</v>
@@ -2340,7 +2346,7 @@
         <v>27</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>99</v>
@@ -2349,21 +2355,21 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>101</v>
@@ -2372,21 +2378,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>103</v>
@@ -2395,21 +2401,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>105</v>
@@ -2418,21 +2424,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>107</v>
@@ -2441,21 +2447,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>109</v>
@@ -2464,21 +2470,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>111</v>
@@ -2487,44 +2493,44 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>114</v>
@@ -2533,21 +2539,21 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>116</v>
@@ -2556,67 +2562,67 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>120</v>
@@ -2625,21 +2631,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>122</v>
@@ -2648,21 +2654,21 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>124</v>
@@ -2671,21 +2677,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>126</v>
@@ -2694,21 +2700,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>128</v>
@@ -2717,21 +2723,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>130</v>
@@ -2740,21 +2746,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>132</v>
@@ -2763,35 +2769,35 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>162</v>
@@ -2800,7 +2806,7 @@
         <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>163</v>
@@ -2809,12 +2815,12 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>164</v>
@@ -2823,7 +2829,7 @@
         <v>27</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>165</v>
@@ -2832,44 +2838,44 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="C92" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>87</v>
@@ -2878,35 +2884,35 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>92</v>
@@ -2915,7 +2921,7 @@
         <v>27</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>93</v>
@@ -2924,12 +2930,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>94</v>
@@ -2938,7 +2944,7 @@
         <v>27</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>95</v>
@@ -2947,12 +2953,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>96</v>
@@ -2961,7 +2967,7 @@
         <v>27</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>97</v>
@@ -2970,12 +2976,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>98</v>
@@ -2984,7 +2990,7 @@
         <v>27</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>99</v>
@@ -2993,21 +2999,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>101</v>
@@ -3016,21 +3022,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>103</v>
@@ -3039,21 +3045,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>105</v>
@@ -3062,21 +3068,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>107</v>
@@ -3085,21 +3091,21 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>109</v>
@@ -3108,21 +3114,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>111</v>
@@ -3131,44 +3137,44 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>114</v>
@@ -3177,21 +3183,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>116</v>
@@ -3200,67 +3206,67 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>120</v>
@@ -3269,21 +3275,21 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>122</v>
@@ -3292,21 +3298,21 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>124</v>
@@ -3315,21 +3321,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>126</v>
@@ -3338,21 +3344,21 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>128</v>
@@ -3361,21 +3367,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>130</v>
@@ -3384,21 +3390,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>132</v>
@@ -3407,35 +3413,35 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>162</v>
@@ -3444,7 +3450,7 @@
         <v>27</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>163</v>
@@ -3453,12 +3459,12 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>164</v>
@@ -3467,7 +3473,7 @@
         <v>27</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>165</v>
@@ -3476,7 +3482,7 @@
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120">
@@ -3484,39 +3490,39 @@
         <v>168</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3527,19 +3533,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3550,7 +3556,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>175</v>
@@ -3559,7 +3565,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>176</v>
@@ -3573,7 +3579,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>177</v>
@@ -3582,7 +3588,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>178</v>
@@ -3596,53 +3602,53 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E126" s="2" t="s">
+      <c r="F126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>186</v>
@@ -3651,7 +3657,7 @@
         <v>27</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>187</v>
@@ -3660,12 +3666,12 @@
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>188</v>
@@ -3674,7 +3680,7 @@
         <v>27</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>189</v>
@@ -3683,12 +3689,12 @@
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>190</v>
@@ -3697,7 +3703,7 @@
         <v>27</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>191</v>
@@ -3706,12 +3712,12 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>192</v>
@@ -3720,7 +3726,7 @@
         <v>27</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>193</v>
@@ -3729,12 +3735,12 @@
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>194</v>
@@ -3743,44 +3749,44 @@
         <v>27</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>197</v>
@@ -3789,44 +3795,44 @@
         <v>27</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>200</v>
@@ -3835,7 +3841,7 @@
         <v>27</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>201</v>
@@ -3844,12 +3850,12 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>202</v>
@@ -3858,7 +3864,7 @@
         <v>27</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>203</v>
@@ -3867,12 +3873,12 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>204</v>
@@ -3881,7 +3887,7 @@
         <v>27</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>205</v>
@@ -3890,44 +3896,44 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>211</v>
@@ -3941,7 +3947,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>212</v>
@@ -3950,7 +3956,7 @@
         <v>27</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>213</v>
@@ -3964,30 +3970,30 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="C141" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D141" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>186</v>
@@ -3996,7 +4002,7 @@
         <v>27</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>187</v>
@@ -4005,12 +4011,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>188</v>
@@ -4019,7 +4025,7 @@
         <v>27</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>189</v>
@@ -4028,12 +4034,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>190</v>
@@ -4042,7 +4048,7 @@
         <v>27</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>191</v>
@@ -4051,12 +4057,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>192</v>
@@ -4065,7 +4071,7 @@
         <v>27</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>193</v>
@@ -4074,12 +4080,12 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>194</v>
@@ -4088,44 +4094,44 @@
         <v>27</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>197</v>
@@ -4134,44 +4140,44 @@
         <v>27</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>200</v>
@@ -4180,7 +4186,7 @@
         <v>27</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>201</v>
@@ -4189,12 +4195,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>202</v>
@@ -4203,7 +4209,7 @@
         <v>27</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>203</v>
@@ -4212,12 +4218,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>204</v>
@@ -4226,7 +4232,7 @@
         <v>27</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>205</v>
@@ -4235,35 +4241,35 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D153" s="2" t="s">
+      <c r="E153" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>186</v>
@@ -4272,7 +4278,7 @@
         <v>27</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>187</v>
@@ -4281,12 +4287,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>188</v>
@@ -4295,7 +4301,7 @@
         <v>27</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>189</v>
@@ -4304,12 +4310,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>190</v>
@@ -4318,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>191</v>
@@ -4327,12 +4333,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>192</v>
@@ -4341,7 +4347,7 @@
         <v>27</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>193</v>
@@ -4350,12 +4356,12 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>194</v>
@@ -4364,44 +4370,44 @@
         <v>27</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>197</v>
@@ -4410,44 +4416,44 @@
         <v>27</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>200</v>
@@ -4456,7 +4462,7 @@
         <v>27</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>201</v>
@@ -4465,12 +4471,12 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>202</v>
@@ -4479,7 +4485,7 @@
         <v>27</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>203</v>
@@ -4488,12 +4494,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>204</v>
@@ -4502,7 +4508,7 @@
         <v>27</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>205</v>
@@ -4511,7 +4517,30 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
         <v>219</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
